--- a/artfynd/A 13322-2022 artfynd.xlsx
+++ b/artfynd/A 13322-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY89"/>
+  <dimension ref="A1:AY91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11253,6 +11253,228 @@
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>114726834</v>
+      </c>
+      <c r="B90" t="n">
+        <v>99761</v>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Godkänd baserat på observatörens uppgifter</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>1365</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Lappranunkel</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Coptidium lapponicum</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>(L.) Tzvelev</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>Krokbäcken, Nästansjö, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q90" t="n">
+        <v>568056</v>
+      </c>
+      <c r="R90" t="n">
+        <v>7193295</v>
+      </c>
+      <c r="S90" t="n">
+        <v>25</v>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>AC-Vil-0126</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>2022-08-05</t>
+        </is>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>2022-08-05</t>
+        </is>
+      </c>
+      <c r="AD90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT90" t="inlineStr"/>
+      <c r="AW90" t="inlineStr">
+        <is>
+          <t>Sofia Lund</t>
+        </is>
+      </c>
+      <c r="AX90" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>114726827</v>
+      </c>
+      <c r="B91" t="n">
+        <v>99761</v>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Godkänd baserat på observatörens uppgifter</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>1365</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Lappranunkel</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Coptidium lapponicum</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>(L.) Tzvelev</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>Krokbäcken, Nästansjö, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q91" t="n">
+        <v>567694</v>
+      </c>
+      <c r="R91" t="n">
+        <v>7192824</v>
+      </c>
+      <c r="S91" t="n">
+        <v>25</v>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>AC-Vil-0131</t>
+        </is>
+      </c>
+      <c r="Y91" t="inlineStr">
+        <is>
+          <t>2022-08-05</t>
+        </is>
+      </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>2022-08-05</t>
+        </is>
+      </c>
+      <c r="AD91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT91" t="inlineStr"/>
+      <c r="AW91" t="inlineStr">
+        <is>
+          <t>Sofia Lund</t>
+        </is>
+      </c>
+      <c r="AX91" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 13322-2022 artfynd.xlsx
+++ b/artfynd/A 13322-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 13322-2022 artfynd.xlsx
+++ b/artfynd/A 13322-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY89"/>
+  <dimension ref="A1:AY88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6979,10 +6979,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>99874901</v>
+        <v>102716788</v>
       </c>
       <c r="B52" t="n">
-        <v>89410</v>
+        <v>78570</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6995,21 +6995,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -7019,10 +7019,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>568462.2830082865</v>
+        <v>567719.6013942137</v>
       </c>
       <c r="R52" t="n">
-        <v>7193530.64736261</v>
+        <v>7192973.404336412</v>
       </c>
       <c r="S52" t="n">
         <v>25</v>
@@ -7049,22 +7049,22 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2022-04-12</t>
+          <t>2022-08-05</t>
         </is>
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2022-04-12</t>
+          <t>2022-08-05</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -7091,10 +7091,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>102716788</v>
+        <v>102716794</v>
       </c>
       <c r="B53" t="n">
-        <v>78570</v>
+        <v>56395</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -7107,34 +7107,39 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Krokbäcken, Nästansjö, Ås lm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>567719.6013942137</v>
+        <v>567637.4947492958</v>
       </c>
       <c r="R53" t="n">
-        <v>7192973.404336412</v>
+        <v>7192892.401277124</v>
       </c>
       <c r="S53" t="n">
         <v>25</v>
@@ -7166,7 +7171,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -7176,7 +7181,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7203,55 +7208,50 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>102716794</v>
+        <v>102716748</v>
       </c>
       <c r="B54" t="n">
-        <v>56395</v>
+        <v>99882</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>1365</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Krokbäcken, Nästansjö, Ås lm</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>567637.4947492958</v>
+        <v>567694</v>
       </c>
       <c r="R54" t="n">
-        <v>7192892.401277124</v>
+        <v>7192824</v>
       </c>
       <c r="S54" t="n">
         <v>25</v>
@@ -7283,7 +7283,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -7293,7 +7293,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7320,37 +7320,37 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>102716748</v>
+        <v>102716759</v>
       </c>
       <c r="B55" t="n">
-        <v>99882</v>
+        <v>89673</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1365</v>
+        <v>658</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Lappranunkel</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Coptidium lapponicum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Tzvelev</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -7360,10 +7360,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>567694</v>
+        <v>567849.3813101366</v>
       </c>
       <c r="R55" t="n">
-        <v>7192824</v>
+        <v>7192811.2233977</v>
       </c>
       <c r="S55" t="n">
         <v>25</v>
@@ -7395,7 +7395,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -7405,7 +7405,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7432,10 +7432,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>102716759</v>
+        <v>102716763</v>
       </c>
       <c r="B56" t="n">
-        <v>89673</v>
+        <v>89577</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7444,25 +7444,25 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>658</v>
+        <v>48</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Romell) Singer</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -7472,10 +7472,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>567849.3813101366</v>
+        <v>567840.1208569881</v>
       </c>
       <c r="R56" t="n">
-        <v>7192811.2233977</v>
+        <v>7192825.05747699</v>
       </c>
       <c r="S56" t="n">
         <v>25</v>
@@ -7507,7 +7507,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7517,7 +7517,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7544,10 +7544,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>102716763</v>
+        <v>102716779</v>
       </c>
       <c r="B57" t="n">
-        <v>89577</v>
+        <v>56395</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7556,38 +7556,43 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>48</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Romell) Singer</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Krokbäcken, Nästansjö, Ås lm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>567840.1208569881</v>
+        <v>568044.2383691776</v>
       </c>
       <c r="R57" t="n">
-        <v>7192825.05747699</v>
+        <v>7193293.504039808</v>
       </c>
       <c r="S57" t="n">
         <v>25</v>
@@ -7619,7 +7624,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7629,7 +7634,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7656,10 +7661,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>102716779</v>
+        <v>102716768</v>
       </c>
       <c r="B58" t="n">
-        <v>56395</v>
+        <v>89403</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7668,43 +7673,38 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>1205</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Krokbäcken, Nästansjö, Ås lm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>568044.2383691776</v>
+        <v>567899.842029657</v>
       </c>
       <c r="R58" t="n">
-        <v>7193293.504039808</v>
+        <v>7192859.60183935</v>
       </c>
       <c r="S58" t="n">
         <v>25</v>
@@ -7736,7 +7736,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7746,7 +7746,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7773,10 +7773,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>102716768</v>
+        <v>102716784</v>
       </c>
       <c r="B59" t="n">
-        <v>89403</v>
+        <v>89410</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7785,25 +7785,25 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1205</v>
+        <v>5432</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7813,10 +7813,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>567899.842029657</v>
+        <v>567796.7253153564</v>
       </c>
       <c r="R59" t="n">
-        <v>7192859.60183935</v>
+        <v>7193029.614455228</v>
       </c>
       <c r="S59" t="n">
         <v>25</v>
@@ -7848,7 +7848,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7858,7 +7858,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7885,10 +7885,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>102716784</v>
+        <v>102716760</v>
       </c>
       <c r="B60" t="n">
-        <v>89410</v>
+        <v>89406</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7901,21 +7901,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>5432</v>
+        <v>1204</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7925,10 +7925,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>567796.7253153564</v>
+        <v>567849.3620730204</v>
       </c>
       <c r="R60" t="n">
-        <v>7193029.614455228</v>
+        <v>7192812.074084461</v>
       </c>
       <c r="S60" t="n">
         <v>25</v>
@@ -7960,7 +7960,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7970,7 +7970,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7997,10 +7997,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>102716760</v>
+        <v>102716764</v>
       </c>
       <c r="B61" t="n">
-        <v>89406</v>
+        <v>89673</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -8013,21 +8013,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1204</v>
+        <v>658</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -8037,10 +8037,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>567849.3620730204</v>
+        <v>567841.3118774476</v>
       </c>
       <c r="R61" t="n">
-        <v>7192812.074084461</v>
+        <v>7192828.914434981</v>
       </c>
       <c r="S61" t="n">
         <v>25</v>
@@ -8072,7 +8072,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -8082,7 +8082,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -8109,10 +8109,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>102716764</v>
+        <v>102716786</v>
       </c>
       <c r="B62" t="n">
-        <v>89673</v>
+        <v>78570</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -8125,21 +8125,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>658</v>
+        <v>2081</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -8149,10 +8149,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>567841.3118774476</v>
+        <v>567769.8019454726</v>
       </c>
       <c r="R62" t="n">
-        <v>7192828.914434981</v>
+        <v>7193033.261452468</v>
       </c>
       <c r="S62" t="n">
         <v>25</v>
@@ -8184,7 +8184,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -8194,7 +8194,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8221,10 +8221,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>102716786</v>
+        <v>102716782</v>
       </c>
       <c r="B63" t="n">
-        <v>78570</v>
+        <v>77506</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -8237,21 +8237,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -8261,10 +8261,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>567769.8019454726</v>
+        <v>567805.5812336213</v>
       </c>
       <c r="R63" t="n">
-        <v>7193033.261452468</v>
+        <v>7193033.644360437</v>
       </c>
       <c r="S63" t="n">
         <v>25</v>
@@ -8296,7 +8296,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -8306,7 +8306,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8333,10 +8333,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>102716782</v>
+        <v>102716783</v>
       </c>
       <c r="B64" t="n">
-        <v>77506</v>
+        <v>78569</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -8349,21 +8349,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -8373,10 +8373,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>567805.5812336213</v>
+        <v>567802.6484876251</v>
       </c>
       <c r="R64" t="n">
-        <v>7193033.644360437</v>
+        <v>7193031.450431921</v>
       </c>
       <c r="S64" t="n">
         <v>25</v>
@@ -8445,10 +8445,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>102716783</v>
+        <v>102716766</v>
       </c>
       <c r="B65" t="n">
-        <v>78569</v>
+        <v>78570</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -8461,21 +8461,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -8485,10 +8485,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>567802.6484876251</v>
+        <v>567887.7737492708</v>
       </c>
       <c r="R65" t="n">
-        <v>7193031.450431921</v>
+        <v>7192865.712057309</v>
       </c>
       <c r="S65" t="n">
         <v>25</v>
@@ -8520,7 +8520,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -8530,7 +8530,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8557,10 +8557,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>102716766</v>
+        <v>102716772</v>
       </c>
       <c r="B66" t="n">
-        <v>78570</v>
+        <v>78503</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8569,25 +8569,25 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>2081</v>
+        <v>6456</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -8597,10 +8597,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>567887.7737492708</v>
+        <v>567934.5330402621</v>
       </c>
       <c r="R66" t="n">
-        <v>7192865.712057309</v>
+        <v>7192889.324702939</v>
       </c>
       <c r="S66" t="n">
         <v>25</v>
@@ -8632,7 +8632,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8642,7 +8642,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8669,10 +8669,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>102716772</v>
+        <v>102716776</v>
       </c>
       <c r="B67" t="n">
-        <v>78503</v>
+        <v>77506</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8681,25 +8681,25 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -8709,10 +8709,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>567934.5330402621</v>
+        <v>568073.2840958816</v>
       </c>
       <c r="R67" t="n">
-        <v>7192889.324702939</v>
+        <v>7193215.02004597</v>
       </c>
       <c r="S67" t="n">
         <v>25</v>
@@ -8744,7 +8744,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8754,7 +8754,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8781,10 +8781,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>102716776</v>
+        <v>102716774</v>
       </c>
       <c r="B68" t="n">
-        <v>77506</v>
+        <v>78596</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8793,25 +8793,25 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -8821,10 +8821,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>568073.2840958816</v>
+        <v>567935.3654787745</v>
       </c>
       <c r="R68" t="n">
-        <v>7193215.02004597</v>
+        <v>7192890.194652664</v>
       </c>
       <c r="S68" t="n">
         <v>25</v>
@@ -8856,7 +8856,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8866,7 +8866,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8893,10 +8893,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>102716774</v>
+        <v>102716747</v>
       </c>
       <c r="B69" t="n">
-        <v>78596</v>
+        <v>96354</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8909,21 +8909,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6462</v>
+        <v>221952</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8933,10 +8933,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>567935.3654787745</v>
+        <v>567697.4292011836</v>
       </c>
       <c r="R69" t="n">
-        <v>7192890.194652664</v>
+        <v>7192823.11119268</v>
       </c>
       <c r="S69" t="n">
         <v>25</v>
@@ -8968,7 +8968,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8978,7 +8978,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -9005,10 +9005,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>102716747</v>
+        <v>102716785</v>
       </c>
       <c r="B70" t="n">
-        <v>96354</v>
+        <v>89406</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -9017,25 +9017,25 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>221952</v>
+        <v>1204</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -9045,10 +9045,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>567697.4292011836</v>
+        <v>567770.8169331191</v>
       </c>
       <c r="R70" t="n">
-        <v>7192823.11119268</v>
+        <v>7193026.050378465</v>
       </c>
       <c r="S70" t="n">
         <v>25</v>
@@ -9080,7 +9080,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -9090,7 +9090,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -9117,10 +9117,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>102716785</v>
+        <v>102716752</v>
       </c>
       <c r="B71" t="n">
-        <v>89406</v>
+        <v>56395</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -9133,34 +9133,39 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>1204</v>
+        <v>100109</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Krokbäcken, Nästansjö, Ås lm</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>567770.8169331191</v>
+        <v>567769.4762646805</v>
       </c>
       <c r="R71" t="n">
-        <v>7193026.050378465</v>
+        <v>7192821.33319346</v>
       </c>
       <c r="S71" t="n">
         <v>25</v>
@@ -9192,7 +9197,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -9202,7 +9207,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -9229,10 +9234,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>102716752</v>
+        <v>102716777</v>
       </c>
       <c r="B72" t="n">
-        <v>56395</v>
+        <v>89410</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -9245,39 +9250,34 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Krokbäcken, Nästansjö, Ås lm</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>567769.4762646805</v>
+        <v>568073.2840958816</v>
       </c>
       <c r="R72" t="n">
-        <v>7192821.33319346</v>
+        <v>7193215.02004597</v>
       </c>
       <c r="S72" t="n">
         <v>25</v>
@@ -9309,7 +9309,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -9319,7 +9319,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9346,10 +9346,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>102716777</v>
+        <v>102716789</v>
       </c>
       <c r="B73" t="n">
-        <v>89410</v>
+        <v>78569</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -9362,21 +9362,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -9386,10 +9386,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>568073.2840958816</v>
+        <v>567719.6013942137</v>
       </c>
       <c r="R73" t="n">
-        <v>7193215.02004597</v>
+        <v>7192973.404336412</v>
       </c>
       <c r="S73" t="n">
         <v>25</v>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -9431,7 +9431,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9458,7 +9458,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>102716789</v>
+        <v>102716757</v>
       </c>
       <c r="B74" t="n">
         <v>78569</v>
@@ -9498,10 +9498,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>567719.6013942137</v>
+        <v>567863.1942120483</v>
       </c>
       <c r="R74" t="n">
-        <v>7192973.404336412</v>
+        <v>7192822.17479571</v>
       </c>
       <c r="S74" t="n">
         <v>25</v>
@@ -9533,7 +9533,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -9543,7 +9543,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9570,10 +9570,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>102716757</v>
+        <v>102716758</v>
       </c>
       <c r="B75" t="n">
-        <v>78569</v>
+        <v>89356</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -9582,25 +9582,25 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -9610,10 +9610,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>567863.1942120483</v>
+        <v>567855.4107011434</v>
       </c>
       <c r="R75" t="n">
-        <v>7192822.17479571</v>
+        <v>7192808.38082188</v>
       </c>
       <c r="S75" t="n">
         <v>25</v>
@@ -9682,10 +9682,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>102716758</v>
+        <v>102716765</v>
       </c>
       <c r="B76" t="n">
-        <v>89356</v>
+        <v>89742</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -9694,25 +9694,25 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>5447</v>
+        <v>1506</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -9722,10 +9722,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>567855.4107011434</v>
+        <v>567835.9515405707</v>
       </c>
       <c r="R76" t="n">
-        <v>7192808.38082188</v>
+        <v>7192839.857734006</v>
       </c>
       <c r="S76" t="n">
         <v>25</v>
@@ -9757,7 +9757,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9767,7 +9767,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9794,37 +9794,37 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>102716765</v>
+        <v>102716778</v>
       </c>
       <c r="B77" t="n">
-        <v>89742</v>
+        <v>99882</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>1506</v>
+        <v>1365</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -9834,10 +9834,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>567835.9515405707</v>
+        <v>568056</v>
       </c>
       <c r="R77" t="n">
-        <v>7192839.857734006</v>
+        <v>7193295</v>
       </c>
       <c r="S77" t="n">
         <v>25</v>
@@ -9869,7 +9869,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9879,7 +9879,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9906,37 +9906,37 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>102716778</v>
+        <v>102716781</v>
       </c>
       <c r="B78" t="n">
-        <v>99882</v>
+        <v>89410</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>1365</v>
+        <v>5432</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Lappranunkel</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Coptidium lapponicum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) Tzvelev</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -9946,10 +9946,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>568056</v>
+        <v>567823.9771016104</v>
       </c>
       <c r="R78" t="n">
-        <v>7193295</v>
+        <v>7193086.825351624</v>
       </c>
       <c r="S78" t="n">
         <v>25</v>
@@ -9981,7 +9981,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9991,7 +9991,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -10018,10 +10018,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>102716781</v>
+        <v>102716750</v>
       </c>
       <c r="B79" t="n">
-        <v>89410</v>
+        <v>89673</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -10034,21 +10034,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -10058,10 +10058,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>567823.9771016104</v>
+        <v>567701.3771056982</v>
       </c>
       <c r="R79" t="n">
-        <v>7193086.825351624</v>
+        <v>7192818.093569417</v>
       </c>
       <c r="S79" t="n">
         <v>25</v>
@@ -10093,7 +10093,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -10103,7 +10103,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -10130,10 +10130,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>102716750</v>
+        <v>102716762</v>
       </c>
       <c r="B80" t="n">
-        <v>89673</v>
+        <v>89392</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -10146,21 +10146,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -10170,10 +10170,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>567701.3771056982</v>
+        <v>567848.4622589125</v>
       </c>
       <c r="R80" t="n">
-        <v>7192818.093569417</v>
+        <v>7192814.181539916</v>
       </c>
       <c r="S80" t="n">
         <v>25</v>
@@ -10205,7 +10205,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -10215,7 +10215,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -10242,10 +10242,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>102716762</v>
+        <v>102716755</v>
       </c>
       <c r="B81" t="n">
-        <v>89392</v>
+        <v>96354</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -10254,25 +10254,25 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>1202</v>
+        <v>221952</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -10282,10 +10282,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>567848.4622589125</v>
+        <v>567872.5484975043</v>
       </c>
       <c r="R81" t="n">
-        <v>7192814.181539916</v>
+        <v>7192785.362481198</v>
       </c>
       <c r="S81" t="n">
         <v>25</v>
@@ -10317,7 +10317,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -10327,7 +10327,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -10354,10 +10354,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>102716755</v>
+        <v>102716756</v>
       </c>
       <c r="B82" t="n">
-        <v>96354</v>
+        <v>90074</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -10370,21 +10370,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>221952</v>
+        <v>3298</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -10394,10 +10394,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>567872.5484975043</v>
+        <v>567863.1942120483</v>
       </c>
       <c r="R82" t="n">
-        <v>7192785.362481198</v>
+        <v>7192822.17479571</v>
       </c>
       <c r="S82" t="n">
         <v>25</v>
@@ -10429,7 +10429,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -10439,7 +10439,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -10466,10 +10466,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>102716756</v>
+        <v>102716771</v>
       </c>
       <c r="B83" t="n">
-        <v>90074</v>
+        <v>78570</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -10478,25 +10478,25 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>3298</v>
+        <v>2081</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -10506,10 +10506,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>567863.1942120483</v>
+        <v>567914.4292092156</v>
       </c>
       <c r="R83" t="n">
-        <v>7192822.17479571</v>
+        <v>7192873.975262483</v>
       </c>
       <c r="S83" t="n">
         <v>25</v>
@@ -10541,7 +10541,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -10551,7 +10551,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -10578,10 +10578,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>102716771</v>
+        <v>102716775</v>
       </c>
       <c r="B84" t="n">
-        <v>78570</v>
+        <v>56395</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -10594,34 +10594,39 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P84" t="inlineStr">
         <is>
           <t>Krokbäcken, Nästansjö, Ås lm</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>567914.4292092156</v>
+        <v>568159.3705239493</v>
       </c>
       <c r="R84" t="n">
-        <v>7192873.975262483</v>
+        <v>7193119.957863194</v>
       </c>
       <c r="S84" t="n">
         <v>25</v>
@@ -10653,7 +10658,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -10663,7 +10668,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -10690,10 +10695,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>102716775</v>
+        <v>102716749</v>
       </c>
       <c r="B85" t="n">
-        <v>56395</v>
+        <v>89406</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -10706,39 +10711,34 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>100109</v>
+        <v>1204</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P85" t="inlineStr">
         <is>
           <t>Krokbäcken, Nästansjö, Ås lm</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>568159.3705239493</v>
+        <v>567694.4002030926</v>
       </c>
       <c r="R85" t="n">
-        <v>7193119.957863194</v>
+        <v>7192825.170640777</v>
       </c>
       <c r="S85" t="n">
         <v>25</v>
@@ -10770,7 +10770,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -10780,7 +10780,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10807,10 +10807,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>102716749</v>
+        <v>102716787</v>
       </c>
       <c r="B86" t="n">
-        <v>89406</v>
+        <v>78569</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -10823,21 +10823,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>1204</v>
+        <v>6458</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -10847,10 +10847,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>567694.4002030926</v>
+        <v>567769.8019454726</v>
       </c>
       <c r="R86" t="n">
-        <v>7192825.170640777</v>
+        <v>7193033.261452468</v>
       </c>
       <c r="S86" t="n">
         <v>25</v>
@@ -10882,7 +10882,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -10892,7 +10892,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10919,10 +10919,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>102716787</v>
+        <v>102716769</v>
       </c>
       <c r="B87" t="n">
-        <v>78569</v>
+        <v>78503</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -10931,25 +10931,25 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -10959,10 +10959,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>567769.8019454726</v>
+        <v>567900.5974795417</v>
       </c>
       <c r="R87" t="n">
-        <v>7193033.261452468</v>
+        <v>7192863.874477708</v>
       </c>
       <c r="S87" t="n">
         <v>25</v>
@@ -10994,7 +10994,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -11004,7 +11004,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -11031,10 +11031,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>102716769</v>
+        <v>102716761</v>
       </c>
       <c r="B88" t="n">
-        <v>78503</v>
+        <v>85703</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -11043,25 +11043,25 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6456</v>
+        <v>510</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Berk. &amp; M.A. Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -11071,10 +11071,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>567900.5974795417</v>
+        <v>567849.3620730204</v>
       </c>
       <c r="R88" t="n">
-        <v>7192863.874477708</v>
+        <v>7192812.074084461</v>
       </c>
       <c r="S88" t="n">
         <v>25</v>
@@ -11106,7 +11106,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -11116,7 +11116,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -11140,118 +11140,6 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
-    </row>
-    <row r="89">
-      <c r="A89" t="n">
-        <v>102716761</v>
-      </c>
-      <c r="B89" t="n">
-        <v>85703</v>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E89" t="n">
-        <v>510</v>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>Doftskinn</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>Cystostereum murrayi</t>
-        </is>
-      </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>(Berk. &amp; M.A. Curtis.) Pouzar</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr"/>
-      <c r="P89" t="inlineStr">
-        <is>
-          <t>Krokbäcken, Nästansjö, Ås lm</t>
-        </is>
-      </c>
-      <c r="Q89" t="n">
-        <v>567849.3620730204</v>
-      </c>
-      <c r="R89" t="n">
-        <v>7192812.074084461</v>
-      </c>
-      <c r="S89" t="n">
-        <v>25</v>
-      </c>
-      <c r="T89" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U89" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="V89" t="inlineStr">
-        <is>
-          <t>Åsele lappmark</t>
-        </is>
-      </c>
-      <c r="W89" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="Y89" t="inlineStr">
-        <is>
-          <t>2022-08-05</t>
-        </is>
-      </c>
-      <c r="Z89" t="inlineStr">
-        <is>
-          <t>16:22</t>
-        </is>
-      </c>
-      <c r="AA89" t="inlineStr">
-        <is>
-          <t>2022-08-05</t>
-        </is>
-      </c>
-      <c r="AB89" t="inlineStr">
-        <is>
-          <t>16:22</t>
-        </is>
-      </c>
-      <c r="AD89" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE89" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG89" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT89" t="inlineStr"/>
-      <c r="AW89" t="inlineStr">
-        <is>
-          <t>Isak Vahlström</t>
-        </is>
-      </c>
-      <c r="AX89" t="inlineStr">
-        <is>
-          <t>Isak Vahlström</t>
-        </is>
-      </c>
-      <c r="AY89" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 13322-2022 artfynd.xlsx
+++ b/artfynd/A 13322-2022 artfynd.xlsx
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>99874871</v>
+        <v>99874935</v>
       </c>
       <c r="B2" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83299</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5447</v>
+        <v>308</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>568847.6642127298</v>
+        <v>568860</v>
       </c>
       <c r="R2" t="n">
-        <v>7193870.462011612</v>
+        <v>7193849</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -750,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -774,17 +769,17 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>granticka</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Porodaedalea chrysoloma s.lat.</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Porodaedalea chrysoloma s.lat.</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -802,15 +797,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>99874907</v>
+        <v>99874880</v>
       </c>
       <c r="B3" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83312</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -818,21 +808,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>1467</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -842,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>568860.0917864562</v>
+        <v>568734</v>
       </c>
       <c r="R3" t="n">
-        <v>7193848.625486347</v>
+        <v>7193943</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -877,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -887,7 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -901,17 +891,17 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>glasbjörk</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Betula pubescens</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Betula pubescens</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -929,37 +919,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>99874908</v>
+        <v>99874871</v>
       </c>
       <c r="B4" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -969,10 +954,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>568735.6995153575</v>
+        <v>568848</v>
       </c>
       <c r="R4" t="n">
-        <v>7193942.341040122</v>
+        <v>7193871</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1004,7 +989,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1014,7 +999,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1056,37 +1041,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>99874935</v>
+        <v>99874908</v>
       </c>
       <c r="B5" t="n">
-        <v>73686</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>308</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1096,10 +1076,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>568860.0917864562</v>
+        <v>568736</v>
       </c>
       <c r="R5" t="n">
-        <v>7193848.625486347</v>
+        <v>7193942</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1131,7 +1111,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1141,7 +1121,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1155,17 +1135,17 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>granticka</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1183,50 +1163,50 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>99874880</v>
+        <v>99874877</v>
       </c>
       <c r="B6" t="n">
-        <v>73698</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1467</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Krokbäcken, Nästansjö, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>568733.5515200808</v>
+        <v>568711</v>
       </c>
       <c r="R6" t="n">
-        <v>7193943.142624542</v>
+        <v>7193905</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1258,7 +1238,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1268,7 +1248,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1279,21 +1259,6 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>glasbjörk</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Betula pubescens</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Betula pubescens</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1310,15 +1275,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>99874877</v>
+        <v>99874873</v>
       </c>
       <c r="B7" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1326,16 +1286,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1355,10 +1315,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>568711.4306567817</v>
+        <v>568838</v>
       </c>
       <c r="R7" t="n">
-        <v>7193904.774240309</v>
+        <v>7193818</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1390,7 +1350,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1400,7 +1360,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1427,15 +1387,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>99874866</v>
+        <v>99874933</v>
       </c>
       <c r="B8" t="n">
-        <v>76504</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83299</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1443,21 +1398,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1467,10 +1422,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>569155.0690341432</v>
+        <v>569293</v>
       </c>
       <c r="R8" t="n">
-        <v>7194374.383747827</v>
+        <v>7194391</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1502,7 +1457,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1512,7 +1467,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1526,17 +1481,17 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>glasbjörk</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Betula pubescens</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Betula pubescens</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1554,15 +1509,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>99874886</v>
+        <v>99874866</v>
       </c>
       <c r="B9" t="n">
-        <v>76863</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78350</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1570,21 +1520,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>498</v>
+        <v>314</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1594,10 +1544,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>568880.9165456441</v>
+        <v>569155</v>
       </c>
       <c r="R9" t="n">
-        <v>7194240.040821896</v>
+        <v>7194374</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1629,7 +1579,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1639,7 +1589,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1681,37 +1631,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>99874927</v>
+        <v>99874867</v>
       </c>
       <c r="B10" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78350</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1312</v>
+        <v>314</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1721,10 +1666,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>569335.5030382421</v>
+        <v>569271</v>
       </c>
       <c r="R10" t="n">
-        <v>7194269.659003499</v>
+        <v>7194160</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1756,7 +1701,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1766,7 +1711,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1808,37 +1753,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>99874914</v>
+        <v>99874885</v>
       </c>
       <c r="B11" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78686</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>498</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1848,10 +1788,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>569141.1307401771</v>
+        <v>568874</v>
       </c>
       <c r="R11" t="n">
-        <v>7194369.383468732</v>
+        <v>7194200</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1883,7 +1823,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1893,7 +1833,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1935,37 +1875,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>99874929</v>
+        <v>99874886</v>
       </c>
       <c r="B12" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78686</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1312</v>
+        <v>498</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1975,10 +1910,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>569208.830158457</v>
+        <v>568881</v>
       </c>
       <c r="R12" t="n">
-        <v>7194093.178740779</v>
+        <v>7194240</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -2010,7 +1945,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2020,7 +1955,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2062,37 +1997,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>99874921</v>
+        <v>99874887</v>
       </c>
       <c r="B13" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78686</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>498</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2102,10 +2032,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>568850.8290164901</v>
+        <v>568952</v>
       </c>
       <c r="R13" t="n">
-        <v>7193769.708810933</v>
+        <v>7194316</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2137,7 +2067,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2147,7 +2077,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2189,37 +2119,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>99874903</v>
+        <v>99874888</v>
       </c>
       <c r="B14" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78686</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>498</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2229,10 +2154,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>569023.6196330723</v>
+        <v>569140</v>
       </c>
       <c r="R14" t="n">
-        <v>7194349.662084485</v>
+        <v>7194371</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2264,7 +2189,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2274,7 +2199,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2316,37 +2241,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>99874913</v>
+        <v>99874890</v>
       </c>
       <c r="B15" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78686</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>498</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2356,10 +2276,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>569105.4313537823</v>
+        <v>569334</v>
       </c>
       <c r="R15" t="n">
-        <v>7194347.718282382</v>
+        <v>7194372</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2391,7 +2311,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2401,7 +2321,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2443,15 +2363,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>99874894</v>
+        <v>99874891</v>
       </c>
       <c r="B16" t="n">
-        <v>77588</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2483,10 +2398,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>569220.4176848246</v>
+        <v>569105</v>
       </c>
       <c r="R16" t="n">
-        <v>7194366.108566319</v>
+        <v>7194347</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2518,7 +2433,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2528,7 +2443,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2570,37 +2485,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>99874888</v>
+        <v>99874892</v>
       </c>
       <c r="B17" t="n">
-        <v>76863</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>498</v>
+        <v>864</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2610,10 +2520,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>569140.2402477085</v>
+        <v>569137</v>
       </c>
       <c r="R17" t="n">
-        <v>7194371.064334808</v>
+        <v>7194366</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2645,7 +2555,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2655,7 +2565,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2697,15 +2607,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>99874897</v>
+        <v>99874893</v>
       </c>
       <c r="B18" t="n">
-        <v>55608</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2713,39 +2618,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>102612</v>
+        <v>864</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Krokbäcken, Nästansjö, Ås lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>569029.4330595188</v>
+        <v>569220</v>
       </c>
       <c r="R18" t="n">
-        <v>7193949.087675139</v>
+        <v>7194366</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2777,7 +2677,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2787,7 +2687,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2798,6 +2698,21 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>glasbjörk</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Betula pubescens</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Betula pubescens</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2814,15 +2729,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>99874872</v>
+        <v>99874895</v>
       </c>
       <c r="B19" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2830,39 +2740,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>864</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Krokbäcken, Nästansjö, Ås lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>569366.5754478904</v>
+        <v>569416</v>
       </c>
       <c r="R19" t="n">
-        <v>7194399.260671999</v>
+        <v>7194446</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2894,7 +2799,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2904,7 +2809,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2915,6 +2820,21 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2931,15 +2851,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>99874867</v>
+        <v>99874924</v>
       </c>
       <c r="B20" t="n">
-        <v>76504</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2947,21 +2862,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>314</v>
+        <v>1312</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2971,10 +2886,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>569270.7440255519</v>
+        <v>569140</v>
       </c>
       <c r="R20" t="n">
-        <v>7194160.117588514</v>
+        <v>7194368</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -3006,7 +2921,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3016,7 +2931,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3058,15 +2973,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>99874869</v>
+        <v>99874925</v>
       </c>
       <c r="B21" t="n">
-        <v>73693</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3074,21 +2984,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6440</v>
+        <v>1312</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -3098,10 +3008,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>568778.1211340926</v>
+        <v>569231</v>
       </c>
       <c r="R21" t="n">
-        <v>7193689.760010699</v>
+        <v>7194344</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -3133,7 +3043,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3143,7 +3053,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3185,15 +3095,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>99874911</v>
+        <v>99874926</v>
       </c>
       <c r="B22" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3201,21 +3106,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3225,10 +3130,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>568886.5493947867</v>
+        <v>569416</v>
       </c>
       <c r="R22" t="n">
-        <v>7194272.923255517</v>
+        <v>7194446</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3260,7 +3165,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3270,7 +3175,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3312,37 +3217,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>99874887</v>
+        <v>99874927</v>
       </c>
       <c r="B23" t="n">
-        <v>76863</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>498</v>
+        <v>1312</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3352,10 +3252,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>568952.0031849314</v>
+        <v>569335</v>
       </c>
       <c r="R23" t="n">
-        <v>7194315.687474321</v>
+        <v>7194270</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3387,7 +3287,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3397,7 +3297,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3439,15 +3339,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>99874876</v>
+        <v>99874928</v>
       </c>
       <c r="B24" t="n">
-        <v>56540</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3455,43 +3350,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103021</v>
+        <v>1312</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Krokbäcken, Nästansjö, Ås lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>569231.5396826513</v>
+        <v>569271</v>
       </c>
       <c r="R24" t="n">
-        <v>7194345.523063817</v>
+        <v>7194157</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3523,7 +3409,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3533,7 +3419,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3544,6 +3430,21 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3560,15 +3461,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>99874926</v>
+        <v>99874929</v>
       </c>
       <c r="B25" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3600,10 +3496,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>569416.2026525026</v>
+        <v>569209</v>
       </c>
       <c r="R25" t="n">
-        <v>7194444.644997349</v>
+        <v>7194093</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3635,7 +3531,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3645,7 +3541,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3687,37 +3583,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>99874904</v>
+        <v>99874870</v>
       </c>
       <c r="B26" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5432</v>
+        <v>5447</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3727,10 +3618,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>569105.8719704481</v>
+        <v>568887</v>
       </c>
       <c r="R26" t="n">
-        <v>7193995.941093843</v>
+        <v>7194273</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3762,7 +3653,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3772,7 +3663,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3814,19 +3705,14 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>99874919</v>
+        <v>99874909</v>
       </c>
       <c r="B27" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
@@ -3854,10 +3740,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>569028.611018372</v>
+        <v>568840</v>
       </c>
       <c r="R27" t="n">
-        <v>7193947.792527781</v>
+        <v>7194112</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3889,7 +3775,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3899,7 +3785,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3941,19 +3827,14 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>99874917</v>
+        <v>99874910</v>
       </c>
       <c r="B28" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
@@ -3981,10 +3862,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>569366.5754478904</v>
+        <v>568874</v>
       </c>
       <c r="R28" t="n">
-        <v>7194399.260671999</v>
+        <v>7194200</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -4016,7 +3897,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -4026,7 +3907,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4068,37 +3949,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>99874925</v>
+        <v>99874911</v>
       </c>
       <c r="B29" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -4108,10 +3984,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>569231.5887607882</v>
+        <v>568887</v>
       </c>
       <c r="R29" t="n">
-        <v>7194343.397425982</v>
+        <v>7194273</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -4143,7 +4019,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4153,7 +4029,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4195,37 +4071,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>99874928</v>
+        <v>99874912</v>
       </c>
       <c r="B30" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -4235,10 +4106,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>569270.8225939712</v>
+        <v>568952</v>
       </c>
       <c r="R30" t="n">
-        <v>7194156.71635724</v>
+        <v>7194316</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -4270,7 +4141,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4280,7 +4151,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4322,19 +4193,14 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>99874910</v>
+        <v>99874913</v>
       </c>
       <c r="B31" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
@@ -4362,10 +4228,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>568874.5982391861</v>
+        <v>569105</v>
       </c>
       <c r="R31" t="n">
-        <v>7194199.910985952</v>
+        <v>7194348</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4397,7 +4263,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4407,7 +4273,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4449,37 +4315,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>99874892</v>
+        <v>99874914</v>
       </c>
       <c r="B32" t="n">
-        <v>77588</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>864</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4489,10 +4350,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>569137.3685886322</v>
+        <v>569141</v>
       </c>
       <c r="R32" t="n">
-        <v>7194366.319269118</v>
+        <v>7194369</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4524,7 +4385,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4534,7 +4395,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4576,19 +4437,14 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>99874916</v>
+        <v>99874915</v>
       </c>
       <c r="B33" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
@@ -4616,10 +4472,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>569300.9192943162</v>
+        <v>569231</v>
       </c>
       <c r="R33" t="n">
-        <v>7194402.421303751</v>
+        <v>7194344</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4651,7 +4507,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4661,7 +4517,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4703,55 +4559,45 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>99874874</v>
+        <v>99874916</v>
       </c>
       <c r="B34" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Krokbäcken, Nästansjö, Ås lm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>568827.8409263557</v>
+        <v>569301</v>
       </c>
       <c r="R34" t="n">
-        <v>7193713.448993189</v>
+        <v>7194402</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4783,7 +4629,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4793,7 +4639,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4804,6 +4650,21 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
@@ -4820,37 +4681,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>99874933</v>
+        <v>99874917</v>
       </c>
       <c r="B35" t="n">
-        <v>73686</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>308</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4860,10 +4716,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>569293.0876388617</v>
+        <v>569367</v>
       </c>
       <c r="R35" t="n">
-        <v>7194391.181277379</v>
+        <v>7194399</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4895,7 +4751,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4905,7 +4761,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4919,17 +4775,17 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>glasbjörk</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
         <is>
-          <t>Betula pubescens</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>Betula pubescens</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -4947,37 +4803,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>99874898</v>
+        <v>99874918</v>
       </c>
       <c r="B36" t="n">
-        <v>73678</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6439</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4987,10 +4838,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>569300.9192943162</v>
+        <v>569268</v>
       </c>
       <c r="R36" t="n">
-        <v>7194402.421303751</v>
+        <v>7194137</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -5022,7 +4873,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -5032,7 +4883,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5046,17 +4897,17 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>glasbjörk</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
         <is>
-          <t>Betula pubescens</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>Betula pubescens</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -5074,37 +4925,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>99874895</v>
+        <v>99874919</v>
       </c>
       <c r="B37" t="n">
-        <v>77588</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>864</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -5114,10 +4960,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>569416.1829687455</v>
+        <v>569029</v>
       </c>
       <c r="R37" t="n">
-        <v>7194445.495224289</v>
+        <v>7193948</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -5149,7 +4995,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5159,7 +5005,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5201,19 +5047,14 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>99874915</v>
+        <v>99874920</v>
       </c>
       <c r="B38" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
@@ -5241,10 +5082,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>569231.5887607882</v>
+        <v>568879</v>
       </c>
       <c r="R38" t="n">
-        <v>7194343.397425982</v>
+        <v>7193872</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -5276,7 +5117,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5286,7 +5127,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5328,15 +5169,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>99874890</v>
+        <v>99874921</v>
       </c>
       <c r="B39" t="n">
-        <v>76863</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5344,21 +5180,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>498</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -5368,10 +5204,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>569333.9950763843</v>
+        <v>568851</v>
       </c>
       <c r="R39" t="n">
-        <v>7194371.710128829</v>
+        <v>7193770</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -5403,7 +5239,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5413,7 +5249,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5455,19 +5291,14 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>99874912</v>
+        <v>99874922</v>
       </c>
       <c r="B40" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
@@ -5495,10 +5326,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>568952.0031849314</v>
+        <v>568774</v>
       </c>
       <c r="R40" t="n">
-        <v>7194315.687474321</v>
+        <v>7193699</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -5530,7 +5361,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5540,7 +5371,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5582,37 +5413,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>99874920</v>
+        <v>99874898</v>
       </c>
       <c r="B41" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83290</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>6439</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5622,10 +5448,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>568879.5730373415</v>
+        <v>569301</v>
       </c>
       <c r="R41" t="n">
-        <v>7193872.045524239</v>
+        <v>7194402</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -5657,7 +5483,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5667,7 +5493,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5681,17 +5507,17 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>glasbjörk</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Betula pubescens</t>
         </is>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Betula pubescens</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5712,12 +5538,7 @@
         <v>99874868</v>
       </c>
       <c r="B42" t="n">
-        <v>73693</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5749,10 +5570,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>569107.9808438232</v>
+        <v>569108</v>
       </c>
       <c r="R42" t="n">
-        <v>7193996.840495347</v>
+        <v>7193997</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -5836,15 +5657,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>99874918</v>
+        <v>99874869</v>
       </c>
       <c r="B43" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5852,21 +5668,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5876,10 +5692,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>569268.2946464564</v>
+        <v>568778</v>
       </c>
       <c r="R43" t="n">
-        <v>7194137.090372855</v>
+        <v>7193690</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -5911,7 +5727,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5921,7 +5737,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5963,15 +5779,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>99874924</v>
+        <v>99874872</v>
       </c>
       <c r="B44" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5979,34 +5790,39 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Krokbäcken, Nästansjö, Ås lm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>569140.3088666237</v>
+        <v>569367</v>
       </c>
       <c r="R44" t="n">
-        <v>7194368.088467157</v>
+        <v>7194399</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -6038,7 +5854,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -6048,7 +5864,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6059,21 +5875,6 @@
       </c>
       <c r="AG44" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ44" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK44" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO44" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
@@ -6090,15 +5891,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>99874884</v>
+        <v>99874874</v>
       </c>
       <c r="B45" t="n">
-        <v>76490</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6106,34 +5902,39 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>228579</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Krokbäcken, Nästansjö, Ås lm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>568776.8244215889</v>
+        <v>568828</v>
       </c>
       <c r="R45" t="n">
-        <v>7193690.581162377</v>
+        <v>7193713</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -6165,7 +5966,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -6175,7 +5976,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6186,21 +5987,6 @@
       </c>
       <c r="AG45" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ45" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK45" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO45" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
@@ -6217,50 +6003,50 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>99874909</v>
+        <v>99874897</v>
       </c>
       <c r="B46" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57132</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Krokbäcken, Nästansjö, Ås lm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>568839.5759189092</v>
+        <v>569030</v>
       </c>
       <c r="R46" t="n">
-        <v>7194111.478900808</v>
+        <v>7193949</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -6292,7 +6078,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -6302,7 +6088,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6313,21 +6099,6 @@
       </c>
       <c r="AG46" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ46" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK46" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO46" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
@@ -6344,15 +6115,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>99874922</v>
+        <v>99874876</v>
       </c>
       <c r="B47" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6360,34 +6126,43 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Krokbäcken, Nästansjö, Ås lm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>568773.6590083888</v>
+        <v>569232</v>
       </c>
       <c r="R47" t="n">
-        <v>7193698.591990191</v>
+        <v>7194345</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -6419,7 +6194,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6429,7 +6204,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6440,21 +6215,6 @@
       </c>
       <c r="AG47" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ47" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK47" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO47" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
@@ -6471,37 +6231,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>99874885</v>
+        <v>99874884</v>
       </c>
       <c r="B48" t="n">
-        <v>76863</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78339</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>498</v>
+        <v>228579</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -6511,10 +6266,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>568874.5982391861</v>
+        <v>568777</v>
       </c>
       <c r="R48" t="n">
-        <v>7194199.910985952</v>
+        <v>7193690</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -6546,7 +6301,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6556,7 +6311,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6598,37 +6353,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>99874870</v>
+        <v>102716763</v>
       </c>
       <c r="B49" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92123</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5447</v>
+        <v>48</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Romell) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6638,10 +6388,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>568886.5493947867</v>
+        <v>567840</v>
       </c>
       <c r="R49" t="n">
-        <v>7194272.923255517</v>
+        <v>7192825</v>
       </c>
       <c r="S49" t="n">
         <v>25</v>
@@ -6668,22 +6418,22 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2022-04-12</t>
+          <t>2022-08-05</t>
         </is>
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2022-04-12</t>
+          <t>2022-08-05</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6694,21 +6444,6 @@
       </c>
       <c r="AG49" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ49" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK49" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO49" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
@@ -6725,15 +6460,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>99874902</v>
+        <v>102716761</v>
       </c>
       <c r="B50" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89292</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6741,21 +6471,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5432</v>
+        <v>510</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6765,10 +6495,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>568839.5759189092</v>
+        <v>567849</v>
       </c>
       <c r="R50" t="n">
-        <v>7194111.478900808</v>
+        <v>7192812</v>
       </c>
       <c r="S50" t="n">
         <v>25</v>
@@ -6795,22 +6525,22 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2022-04-12</t>
+          <t>2022-08-05</t>
         </is>
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2022-04-12</t>
+          <t>2022-08-05</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6821,21 +6551,6 @@
       </c>
       <c r="AG50" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ50" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK50" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO50" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
@@ -6852,15 +6567,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>99874891</v>
+        <v>102716750</v>
       </c>
       <c r="B51" t="n">
-        <v>77588</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6868,21 +6578,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>864</v>
+        <v>658</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6892,10 +6602,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>569105.4509492764</v>
+        <v>567702</v>
       </c>
       <c r="R51" t="n">
-        <v>7194346.868028226</v>
+        <v>7192818</v>
       </c>
       <c r="S51" t="n">
         <v>25</v>
@@ -6922,22 +6632,22 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2022-04-12</t>
+          <t>2022-08-05</t>
         </is>
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2022-04-12</t>
+          <t>2022-08-05</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6948,21 +6658,6 @@
       </c>
       <c r="AG51" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ51" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK51" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO51" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
@@ -6979,15 +6674,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>102716788</v>
+        <v>102716759</v>
       </c>
       <c r="B52" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6995,21 +6685,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>2081</v>
+        <v>658</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -7019,10 +6709,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>567719.6013942137</v>
+        <v>567850</v>
       </c>
       <c r="R52" t="n">
-        <v>7192973.404336412</v>
+        <v>7192811</v>
       </c>
       <c r="S52" t="n">
         <v>25</v>
@@ -7054,7 +6744,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -7064,7 +6754,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -7091,15 +6781,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>102716794</v>
+        <v>102716764</v>
       </c>
       <c r="B53" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -7107,39 +6792,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Krokbäcken, Nästansjö, Ås lm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>567637.4947492958</v>
+        <v>567841</v>
       </c>
       <c r="R53" t="n">
-        <v>7192892.401277124</v>
+        <v>7192829</v>
       </c>
       <c r="S53" t="n">
         <v>25</v>
@@ -7171,7 +6851,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -7181,7 +6861,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7208,37 +6888,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>102716748</v>
+        <v>102716762</v>
       </c>
       <c r="B54" t="n">
-        <v>99882</v>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1365</v>
+        <v>1202</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Lappranunkel</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Coptidium lapponicum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Tzvelev</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -7248,10 +6923,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>567694</v>
+        <v>567848</v>
       </c>
       <c r="R54" t="n">
-        <v>7192824</v>
+        <v>7192814</v>
       </c>
       <c r="S54" t="n">
         <v>25</v>
@@ -7283,7 +6958,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -7293,7 +6968,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7320,37 +6995,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>102716759</v>
+        <v>102716749</v>
       </c>
       <c r="B55" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>658</v>
+        <v>1204</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -7360,10 +7030,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>567849.3813101366</v>
+        <v>567694</v>
       </c>
       <c r="R55" t="n">
-        <v>7192811.2233977</v>
+        <v>7192825</v>
       </c>
       <c r="S55" t="n">
         <v>25</v>
@@ -7395,7 +7065,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -7405,7 +7075,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7432,15 +7102,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>102716763</v>
+        <v>102716760</v>
       </c>
       <c r="B56" t="n">
-        <v>89577</v>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7448,21 +7113,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>48</v>
+        <v>1204</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Romell) Singer</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -7472,10 +7137,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>567840.1208569881</v>
+        <v>567849</v>
       </c>
       <c r="R56" t="n">
-        <v>7192825.05747699</v>
+        <v>7192812</v>
       </c>
       <c r="S56" t="n">
         <v>25</v>
@@ -7507,7 +7172,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7517,7 +7182,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7544,55 +7209,45 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>102716779</v>
+        <v>102716785</v>
       </c>
       <c r="B57" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>1204</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Krokbäcken, Nästansjö, Ås lm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>568044.2383691776</v>
+        <v>567771</v>
       </c>
       <c r="R57" t="n">
-        <v>7193293.504039808</v>
+        <v>7193026</v>
       </c>
       <c r="S57" t="n">
         <v>25</v>
@@ -7624,7 +7279,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7634,7 +7289,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7664,12 +7319,7 @@
         <v>102716768</v>
       </c>
       <c r="B58" t="n">
-        <v>89403</v>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91920</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7701,10 +7351,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>567899.842029657</v>
+        <v>567900</v>
       </c>
       <c r="R58" t="n">
-        <v>7192859.60183935</v>
+        <v>7192860</v>
       </c>
       <c r="S58" t="n">
         <v>25</v>
@@ -7773,37 +7423,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>102716784</v>
+        <v>102716748</v>
       </c>
       <c r="B59" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101299</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>5432</v>
+        <v>1365</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7813,10 +7458,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>567796.7253153564</v>
+        <v>567694</v>
       </c>
       <c r="R59" t="n">
-        <v>7193029.614455228</v>
+        <v>7192824</v>
       </c>
       <c r="S59" t="n">
         <v>25</v>
@@ -7848,7 +7493,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7858,7 +7503,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7885,37 +7530,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>102716760</v>
+        <v>102716778</v>
       </c>
       <c r="B60" t="n">
-        <v>89406</v>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101299</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1204</v>
+        <v>1365</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7925,10 +7565,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>567849.3620730204</v>
+        <v>568056</v>
       </c>
       <c r="R60" t="n">
-        <v>7192812.074084461</v>
+        <v>7193295</v>
       </c>
       <c r="S60" t="n">
         <v>25</v>
@@ -7960,7 +7600,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7970,7 +7610,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7997,37 +7637,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>102716764</v>
+        <v>102716765</v>
       </c>
       <c r="B61" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92292</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>658</v>
+        <v>1506</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -8037,10 +7672,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>567841.3118774476</v>
+        <v>567836</v>
       </c>
       <c r="R61" t="n">
-        <v>7192828.914434981</v>
+        <v>7192840</v>
       </c>
       <c r="S61" t="n">
         <v>25</v>
@@ -8109,15 +7744,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>102716786</v>
+        <v>102716766</v>
       </c>
       <c r="B62" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -8149,10 +7779,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>567769.8019454726</v>
+        <v>567888</v>
       </c>
       <c r="R62" t="n">
-        <v>7193033.261452468</v>
+        <v>7192866</v>
       </c>
       <c r="S62" t="n">
         <v>25</v>
@@ -8184,7 +7814,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -8194,7 +7824,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8221,15 +7851,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>102716782</v>
+        <v>102716771</v>
       </c>
       <c r="B63" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8237,21 +7862,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -8261,10 +7886,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>567805.5812336213</v>
+        <v>567915</v>
       </c>
       <c r="R63" t="n">
-        <v>7193033.644360437</v>
+        <v>7192874</v>
       </c>
       <c r="S63" t="n">
         <v>25</v>
@@ -8296,7 +7921,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -8306,7 +7931,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8333,15 +7958,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>102716783</v>
+        <v>102716786</v>
       </c>
       <c r="B64" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8349,21 +7969,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -8373,10 +7993,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>567802.6484876251</v>
+        <v>567770</v>
       </c>
       <c r="R64" t="n">
-        <v>7193031.450431921</v>
+        <v>7193033</v>
       </c>
       <c r="S64" t="n">
         <v>25</v>
@@ -8408,7 +8028,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -8418,7 +8038,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8445,15 +8065,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>102716766</v>
+        <v>102716788</v>
       </c>
       <c r="B65" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8485,10 +8100,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>567887.7737492708</v>
+        <v>567719</v>
       </c>
       <c r="R65" t="n">
-        <v>7192865.712057309</v>
+        <v>7192974</v>
       </c>
       <c r="S65" t="n">
         <v>25</v>
@@ -8520,7 +8135,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -8530,7 +8145,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8557,37 +8172,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>102716772</v>
+        <v>102716790</v>
       </c>
       <c r="B66" t="n">
-        <v>78503</v>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6456</v>
+        <v>2081</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -8597,10 +8207,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>567934.5330402621</v>
+        <v>567702</v>
       </c>
       <c r="R66" t="n">
-        <v>7192889.324702939</v>
+        <v>7192971</v>
       </c>
       <c r="S66" t="n">
         <v>25</v>
@@ -8632,7 +8242,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8642,7 +8252,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8669,37 +8279,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>102716776</v>
+        <v>102716756</v>
       </c>
       <c r="B67" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92632</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -8709,10 +8314,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>568073.2840958816</v>
+        <v>567863</v>
       </c>
       <c r="R67" t="n">
-        <v>7193215.02004597</v>
+        <v>7192822</v>
       </c>
       <c r="S67" t="n">
         <v>25</v>
@@ -8744,7 +8349,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8754,7 +8359,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8781,15 +8386,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>102716774</v>
+        <v>102716758</v>
       </c>
       <c r="B68" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8797,21 +8397,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6462</v>
+        <v>5447</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -8821,10 +8421,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>567935.3654787745</v>
+        <v>567856</v>
       </c>
       <c r="R68" t="n">
-        <v>7192890.194652664</v>
+        <v>7192808</v>
       </c>
       <c r="S68" t="n">
         <v>25</v>
@@ -8856,7 +8456,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8866,7 +8466,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8893,37 +8493,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>102716747</v>
+        <v>102716776</v>
       </c>
       <c r="B69" t="n">
-        <v>96354</v>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8933,10 +8528,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>567697.4292011836</v>
+        <v>568073</v>
       </c>
       <c r="R69" t="n">
-        <v>7192823.11119268</v>
+        <v>7193215</v>
       </c>
       <c r="S69" t="n">
         <v>25</v>
@@ -8968,7 +8563,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8978,7 +8573,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -9005,37 +8600,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>102716785</v>
+        <v>102716782</v>
       </c>
       <c r="B70" t="n">
-        <v>89406</v>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -9045,10 +8635,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>567770.8169331191</v>
+        <v>567805</v>
       </c>
       <c r="R70" t="n">
-        <v>7193026.050378465</v>
+        <v>7193033</v>
       </c>
       <c r="S70" t="n">
         <v>25</v>
@@ -9080,7 +8670,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -9090,7 +8680,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -9117,55 +8707,45 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>102716752</v>
+        <v>102716769</v>
       </c>
       <c r="B71" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100109</v>
+        <v>6456</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Krokbäcken, Nästansjö, Ås lm</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>567769.4762646805</v>
+        <v>567901</v>
       </c>
       <c r="R71" t="n">
-        <v>7192821.33319346</v>
+        <v>7192864</v>
       </c>
       <c r="S71" t="n">
         <v>25</v>
@@ -9197,7 +8777,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -9207,7 +8787,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -9234,37 +8814,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>102716777</v>
+        <v>102716772</v>
       </c>
       <c r="B72" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>5432</v>
+        <v>6456</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -9274,10 +8849,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>568073.2840958816</v>
+        <v>567934</v>
       </c>
       <c r="R72" t="n">
-        <v>7193215.02004597</v>
+        <v>7192889</v>
       </c>
       <c r="S72" t="n">
         <v>25</v>
@@ -9309,7 +8884,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -9319,7 +8894,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9346,15 +8921,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>102716789</v>
+        <v>102716757</v>
       </c>
       <c r="B73" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9386,10 +8956,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>567719.6013942137</v>
+        <v>567863</v>
       </c>
       <c r="R73" t="n">
-        <v>7192973.404336412</v>
+        <v>7192822</v>
       </c>
       <c r="S73" t="n">
         <v>25</v>
@@ -9421,7 +8991,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -9431,7 +9001,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9458,15 +9028,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>102716757</v>
+        <v>102716783</v>
       </c>
       <c r="B74" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9498,10 +9063,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>567863.1942120483</v>
+        <v>567802</v>
       </c>
       <c r="R74" t="n">
-        <v>7192822.17479571</v>
+        <v>7193032</v>
       </c>
       <c r="S74" t="n">
         <v>25</v>
@@ -9533,7 +9098,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -9543,7 +9108,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9570,37 +9135,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>102716758</v>
+        <v>102716787</v>
       </c>
       <c r="B75" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -9610,10 +9170,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>567855.4107011434</v>
+        <v>567770</v>
       </c>
       <c r="R75" t="n">
-        <v>7192808.38082188</v>
+        <v>7193033</v>
       </c>
       <c r="S75" t="n">
         <v>25</v>
@@ -9645,7 +9205,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -9655,7 +9215,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9682,37 +9242,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>102716765</v>
+        <v>102716789</v>
       </c>
       <c r="B76" t="n">
-        <v>89742</v>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>1506</v>
+        <v>6458</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -9722,10 +9277,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>567835.9515405707</v>
+        <v>567719</v>
       </c>
       <c r="R76" t="n">
-        <v>7192839.857734006</v>
+        <v>7192974</v>
       </c>
       <c r="S76" t="n">
         <v>25</v>
@@ -9757,7 +9312,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9767,7 +9322,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9794,37 +9349,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>102716778</v>
+        <v>102716791</v>
       </c>
       <c r="B77" t="n">
-        <v>99882</v>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>1365</v>
+        <v>6458</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Lappranunkel</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Coptidium lapponicum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) Tzvelev</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -9834,10 +9384,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>568056</v>
+        <v>567695</v>
       </c>
       <c r="R77" t="n">
-        <v>7193295</v>
+        <v>7192976</v>
       </c>
       <c r="S77" t="n">
         <v>25</v>
@@ -9869,7 +9419,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9879,7 +9429,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9906,37 +9456,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>102716781</v>
+        <v>102716774</v>
       </c>
       <c r="B78" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>5432</v>
+        <v>6462</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -9946,10 +9491,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>567823.9771016104</v>
+        <v>567935</v>
       </c>
       <c r="R78" t="n">
-        <v>7193086.825351624</v>
+        <v>7192890</v>
       </c>
       <c r="S78" t="n">
         <v>25</v>
@@ -9981,7 +9526,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9991,7 +9536,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -10018,15 +9563,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>102716750</v>
+        <v>102716752</v>
       </c>
       <c r="B79" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -10034,34 +9574,39 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P79" t="inlineStr">
         <is>
           <t>Krokbäcken, Nästansjö, Ås lm</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>567701.3771056982</v>
+        <v>567769</v>
       </c>
       <c r="R79" t="n">
-        <v>7192818.093569417</v>
+        <v>7192821</v>
       </c>
       <c r="S79" t="n">
         <v>25</v>
@@ -10093,7 +9638,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -10103,7 +9648,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -10130,15 +9675,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>102716762</v>
+        <v>102716775</v>
       </c>
       <c r="B80" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -10146,34 +9686,39 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Krokbäcken, Nästansjö, Ås lm</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>567848.4622589125</v>
+        <v>568160</v>
       </c>
       <c r="R80" t="n">
-        <v>7192814.181539916</v>
+        <v>7193120</v>
       </c>
       <c r="S80" t="n">
         <v>25</v>
@@ -10205,7 +9750,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -10215,7 +9760,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -10242,50 +9787,50 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>102716755</v>
+        <v>102716779</v>
       </c>
       <c r="B81" t="n">
-        <v>96354</v>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P81" t="inlineStr">
         <is>
           <t>Krokbäcken, Nästansjö, Ås lm</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>567872.5484975043</v>
+        <v>568044</v>
       </c>
       <c r="R81" t="n">
-        <v>7192785.362481198</v>
+        <v>7193293</v>
       </c>
       <c r="S81" t="n">
         <v>25</v>
@@ -10317,7 +9862,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -10327,7 +9872,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -10354,50 +9899,50 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>102716756</v>
+        <v>102716780</v>
       </c>
       <c r="B82" t="n">
-        <v>90074</v>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P82" t="inlineStr">
         <is>
           <t>Krokbäcken, Nästansjö, Ås lm</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>567863.1942120483</v>
+        <v>567948</v>
       </c>
       <c r="R82" t="n">
-        <v>7192822.17479571</v>
+        <v>7193253</v>
       </c>
       <c r="S82" t="n">
         <v>25</v>
@@ -10429,7 +9974,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -10439,7 +9984,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -10466,15 +10011,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>102716771</v>
+        <v>102716792</v>
       </c>
       <c r="B83" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10482,34 +10022,39 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P83" t="inlineStr">
         <is>
           <t>Krokbäcken, Nästansjö, Ås lm</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>567914.4292092156</v>
+        <v>567671</v>
       </c>
       <c r="R83" t="n">
-        <v>7192873.975262483</v>
+        <v>7192938</v>
       </c>
       <c r="S83" t="n">
         <v>25</v>
@@ -10541,7 +10086,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -10551,7 +10096,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -10578,15 +10123,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>102716775</v>
+        <v>102716793</v>
       </c>
       <c r="B84" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10614,7 +10154,7 @@
       <c r="I84" t="inlineStr"/>
       <c r="M84" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P84" t="inlineStr">
@@ -10623,10 +10163,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>568159.3705239493</v>
+        <v>567659</v>
       </c>
       <c r="R84" t="n">
-        <v>7193119.957863194</v>
+        <v>7192933</v>
       </c>
       <c r="S84" t="n">
         <v>25</v>
@@ -10658,7 +10198,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -10668,7 +10208,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -10695,15 +10235,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>102716749</v>
+        <v>102716794</v>
       </c>
       <c r="B85" t="n">
-        <v>89406</v>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10711,34 +10246,39 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>1204</v>
+        <v>100109</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P85" t="inlineStr">
         <is>
           <t>Krokbäcken, Nästansjö, Ås lm</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>567694.4002030926</v>
+        <v>567638</v>
       </c>
       <c r="R85" t="n">
-        <v>7192825.170640777</v>
+        <v>7192892</v>
       </c>
       <c r="S85" t="n">
         <v>25</v>
@@ -10770,7 +10310,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -10780,7 +10320,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10807,15 +10347,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>102716787</v>
+        <v>102716795</v>
       </c>
       <c r="B86" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10823,34 +10358,39 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P86" t="inlineStr">
         <is>
           <t>Krokbäcken, Nästansjö, Ås lm</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>567769.8019454726</v>
+        <v>567628</v>
       </c>
       <c r="R86" t="n">
-        <v>7193033.261452468</v>
+        <v>7192899</v>
       </c>
       <c r="S86" t="n">
         <v>25</v>
@@ -10882,7 +10422,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -10892,7 +10432,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10919,15 +10459,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>102716769</v>
+        <v>102716747</v>
       </c>
       <c r="B87" t="n">
-        <v>78503</v>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99140</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10935,21 +10470,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6456</v>
+        <v>221952</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -10959,10 +10494,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>567900.5974795417</v>
+        <v>567697</v>
       </c>
       <c r="R87" t="n">
-        <v>7192863.874477708</v>
+        <v>7192823</v>
       </c>
       <c r="S87" t="n">
         <v>25</v>
@@ -10994,7 +10529,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -11004,7 +10539,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -11031,37 +10566,32 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>102716761</v>
+        <v>102716755</v>
       </c>
       <c r="B88" t="n">
-        <v>85703</v>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99140</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>510</v>
+        <v>221952</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A. Curtis.) Pouzar</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -11071,10 +10601,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>567849.3620730204</v>
+        <v>567873</v>
       </c>
       <c r="R88" t="n">
-        <v>7192812.074084461</v>
+        <v>7192786</v>
       </c>
       <c r="S88" t="n">
         <v>25</v>
@@ -11106,7 +10636,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -11116,7 +10646,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AD88" t="b">
